--- a/web/src/main/webapp/StorageYard/Other/UserDoc/SalaryGenerate/SalaryExcelUpload1.xlsx
+++ b/web/src/main/webapp/StorageYard/Other/UserDoc/SalaryGenerate/SalaryExcelUpload1.xlsx
@@ -399,10 +399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
